--- a/research/traditional_assets/database/data/philippines/philippines_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0339</v>
+        <v>0.05075</v>
       </c>
       <c r="E2">
-        <v>-0.126</v>
+        <v>-0.011</v>
       </c>
       <c r="G2">
-        <v>0.06646686324745009</v>
+        <v>0.07767929443750296</v>
       </c>
       <c r="H2">
-        <v>0.06646686324745009</v>
+        <v>0.07767929443750296</v>
       </c>
       <c r="I2">
-        <v>0.06445271587631524</v>
+        <v>0.06668694145106387</v>
       </c>
       <c r="J2">
-        <v>0.0460234016188493</v>
+        <v>0.05618045807840951</v>
       </c>
       <c r="K2">
-        <v>37.046</v>
+        <v>67.75999999999999</v>
       </c>
       <c r="L2">
-        <v>0.1492322070221234</v>
+        <v>0.2482806127870378</v>
       </c>
       <c r="M2">
-        <v>37.932</v>
+        <v>39.88</v>
       </c>
       <c r="N2">
-        <v>0.04254374158815612</v>
+        <v>0.0570610960080126</v>
       </c>
       <c r="O2">
-        <v>1.023916212276629</v>
+        <v>0.5885478158205432</v>
       </c>
       <c r="P2">
-        <v>37.932</v>
+        <v>31.26</v>
       </c>
       <c r="Q2">
-        <v>0.04254374158815612</v>
+        <v>0.04472742881671198</v>
       </c>
       <c r="R2">
-        <v>1.023916212276629</v>
+        <v>0.4613341204250296</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.216148445336008</v>
       </c>
       <c r="U2">
-        <v>68.749</v>
+        <v>82.12599999999999</v>
       </c>
       <c r="V2">
-        <v>0.07710744728577837</v>
+        <v>0.1175075118042638</v>
       </c>
       <c r="W2">
-        <v>0.03252019465858101</v>
+        <v>0.04406206083362657</v>
       </c>
       <c r="X2">
-        <v>0.0268126265289888</v>
+        <v>0.05333114413526974</v>
       </c>
       <c r="Y2">
-        <v>0.005707568129592215</v>
+        <v>-0.009269083301643166</v>
       </c>
       <c r="Z2">
-        <v>0.2483661961685149</v>
+        <v>0.3155244790817642</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.02693958762427644</v>
+        <v>0.05333080955830185</v>
       </c>
       <c r="AC2">
-        <v>-0.02692799772381003</v>
+        <v>-0.05332185234529718</v>
       </c>
       <c r="AD2">
-        <v>130.748</v>
+        <v>130.295</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>130.748</v>
+        <v>130.295</v>
       </c>
       <c r="AG2">
-        <v>61.999</v>
+        <v>48.16900000000003</v>
       </c>
       <c r="AH2">
-        <v>0.127889916153795</v>
+        <v>0.1571343290782024</v>
       </c>
       <c r="AI2">
-        <v>0.1373608248289135</v>
+        <v>0.1500653609826607</v>
       </c>
       <c r="AJ2">
-        <v>0.06501579804509022</v>
+        <v>0.06447731066340597</v>
       </c>
       <c r="AK2">
-        <v>0.07020537668623011</v>
+        <v>0.06127365864889863</v>
       </c>
       <c r="AL2">
-        <v>0.067</v>
+        <v>0.036</v>
       </c>
       <c r="AM2">
-        <v>-2.193</v>
+        <v>-2.064</v>
       </c>
       <c r="AN2">
-        <v>7.144699453551912</v>
+        <v>6.450247524752476</v>
       </c>
       <c r="AO2">
-        <v>238.8059701492537</v>
+        <v>505.5555555555556</v>
       </c>
       <c r="AP2">
-        <v>3.387923497267759</v>
+        <v>2.384603960396041</v>
       </c>
       <c r="AQ2">
-        <v>-7.295941632466942</v>
+        <v>-8.81782945736434</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0593</v>
+        <v>0.0547</v>
       </c>
       <c r="E3">
-        <v>0.0281</v>
+        <v>-0.011</v>
       </c>
       <c r="G3">
-        <v>0.5518394648829432</v>
+        <v>0.7114093959731543</v>
       </c>
       <c r="H3">
-        <v>0.5518394648829432</v>
+        <v>0.7114093959731543</v>
       </c>
       <c r="I3">
-        <v>0.5351170568561873</v>
+        <v>0.6107382550335571</v>
       </c>
       <c r="J3">
-        <v>0.3994711052345026</v>
+        <v>0.4586833183422127</v>
       </c>
       <c r="K3">
-        <v>16.1</v>
+        <v>14.7</v>
       </c>
       <c r="L3">
-        <v>0.5384615384615385</v>
+        <v>0.4932885906040268</v>
       </c>
       <c r="M3">
-        <v>12.8</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="N3">
-        <v>0.0375697094217787</v>
+        <v>0.04086393088552916</v>
       </c>
       <c r="O3">
-        <v>0.7950310559006211</v>
+        <v>0.6435374149659865</v>
       </c>
       <c r="P3">
-        <v>12.8</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="Q3">
-        <v>0.0375697094217787</v>
+        <v>0.04086393088552916</v>
       </c>
       <c r="R3">
-        <v>0.7950310559006211</v>
+        <v>0.6435374149659865</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.8</v>
+        <v>15.6</v>
       </c>
       <c r="V3">
-        <v>0.01702377458174347</v>
+        <v>0.06738660907127429</v>
       </c>
       <c r="W3">
-        <v>0.1501865671641791</v>
+        <v>0.1402671755725191</v>
       </c>
       <c r="X3">
-        <v>0.02664860200015233</v>
+        <v>0.0533404359252423</v>
       </c>
       <c r="Y3">
-        <v>0.1235379651640268</v>
+        <v>0.08692673964727679</v>
       </c>
       <c r="Z3">
-        <v>0.4507764209256747</v>
+        <v>0.2983938799214964</v>
       </c>
       <c r="AA3">
-        <v>0.1800721550808326</v>
+        <v>0.1368682950153997</v>
       </c>
       <c r="AB3">
-        <v>0.02665122283733722</v>
+        <v>0.05333976677130652</v>
       </c>
       <c r="AC3">
-        <v>0.1534209322434954</v>
+        <v>0.08352852824409319</v>
       </c>
       <c r="AD3">
-        <v>0.868</v>
+        <v>0.395</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.868</v>
+        <v>0.395</v>
       </c>
       <c r="AG3">
-        <v>-4.931999999999999</v>
+        <v>-15.205</v>
       </c>
       <c r="AH3">
-        <v>0.002541221660108675</v>
+        <v>0.001703357122835766</v>
       </c>
       <c r="AI3">
-        <v>0.00821440738918121</v>
+        <v>0.004394015240002225</v>
       </c>
       <c r="AJ3">
-        <v>-0.01468871363560554</v>
+        <v>-0.07029751034466816</v>
       </c>
       <c r="AK3">
-        <v>-0.04938518844875235</v>
+        <v>-0.2046571101689212</v>
       </c>
       <c r="AL3">
-        <v>0.067</v>
+        <v>0.036</v>
       </c>
       <c r="AM3">
-        <v>-2.193</v>
+        <v>-2.064</v>
       </c>
       <c r="AN3">
-        <v>0.04743169398907104</v>
+        <v>0.01955445544554455</v>
       </c>
       <c r="AO3">
-        <v>238.8059701492537</v>
+        <v>505.5555555555556</v>
       </c>
       <c r="AP3">
-        <v>-0.2695081967213114</v>
+        <v>-0.7527227722772277</v>
       </c>
       <c r="AQ3">
-        <v>-7.295941632466942</v>
+        <v>-8.81782945736434</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ferronoux Holdings, Inc. (PSE:FERRO)</t>
+          <t>Citystate Savings Bank, Inc. (PSE:CSB)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -855,6 +855,9 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.102</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -868,19 +871,19 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0.132</v>
+        <v>-0.267</v>
       </c>
       <c r="L4">
-        <v>1.590361445783133</v>
+        <v>-0.04635416666666667</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.3780701754385964</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>-32.28464419475655</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -889,37 +892,40 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>8.619999999999999</v>
+      </c>
+      <c r="T4">
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>0.005</v>
+        <v>3.72</v>
       </c>
       <c r="V4">
-        <v>0.0002958579881656805</v>
+        <v>0.1631578947368421</v>
       </c>
       <c r="W4">
-        <v>0.04925373134328358</v>
+        <v>-0.01160869565217391</v>
       </c>
       <c r="X4">
-        <v>0.0266280430364044</v>
+        <v>0.05332185234529718</v>
       </c>
       <c r="Y4">
-        <v>0.02262568830687919</v>
+        <v>-0.0649305479974711</v>
       </c>
       <c r="Z4">
-        <v>0.03110944527736132</v>
+        <v>0.2862823061630219</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.0266280430364044</v>
+        <v>0.05332185234529718</v>
       </c>
       <c r="AC4">
-        <v>-0.0266280430364044</v>
+        <v>-0.05332185234529718</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -931,7 +937,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.005</v>
+        <v>-3.72</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -940,10 +946,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.0002959455460195324</v>
+        <v>-0.1949685534591195</v>
       </c>
       <c r="AK4">
-        <v>-0.001869158878504673</v>
+        <v>-0.2403100775193799</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -960,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prime Media Holdings, Inc. (PSE:PRIM)</t>
+          <t>Ferronoux Holdings, Inc. (PSE:FERRO)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -969,7 +975,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.314</v>
+        <v>-0.225</v>
+      </c>
+      <c r="E5">
+        <v>-0.305</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -984,10 +993,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>-0.06</v>
+        <v>0.027</v>
       </c>
       <c r="L5">
-        <v>-1.176470588235294</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -996,7 +1005,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1005,37 +1014,37 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.144</v>
+        <v>0.006</v>
       </c>
       <c r="V5">
-        <v>0.009056603773584904</v>
+        <v>0.0005263157894736842</v>
       </c>
       <c r="W5">
-        <v>0.01840490797546012</v>
+        <v>0.01007462686567164</v>
       </c>
       <c r="X5">
-        <v>0.0266280430364044</v>
+        <v>0.05332185234529718</v>
       </c>
       <c r="Y5">
-        <v>-0.008223135060944273</v>
+        <v>-0.04324722547962554</v>
       </c>
       <c r="Z5">
-        <v>-0.01613924050632911</v>
+        <v>0.02130841121495327</v>
       </c>
       <c r="AA5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.0266280430364044</v>
+        <v>0.05332185234529718</v>
       </c>
       <c r="AC5">
-        <v>-0.0266280430364044</v>
+        <v>-0.05332185234529718</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1047,19 +1056,19 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.144</v>
+        <v>-0.006</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AI5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.009139375476009138</v>
+        <v>-0.000526592943654555</v>
       </c>
       <c r="AK5">
-        <v>0.0477770404777704</v>
+        <v>-0.002548853016142736</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1076,7 +1085,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Citystate Savings Bank, Inc. (PSE:CSB)</t>
+          <t>Philippine Savings Bank (PSE:PSB)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1085,7 +1094,10 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0339</v>
+        <v>0.04679999999999999</v>
+      </c>
+      <c r="E6">
+        <v>0.0493</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1100,331 +1112,90 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0.18</v>
+        <v>53.3</v>
       </c>
       <c r="L6">
-        <v>0.03180212014134275</v>
+        <v>0.2246101980615255</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>21.8</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.05032317636195753</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>0.4090056285178237</v>
       </c>
       <c r="P6">
-        <v>-0</v>
+        <v>21.8</v>
       </c>
       <c r="Q6">
-        <v>-0</v>
+        <v>0.05032317636195753</v>
       </c>
       <c r="R6">
-        <v>-0</v>
+        <v>0.4090056285178237</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
       <c r="U6">
-        <v>3.96</v>
+        <v>62.8</v>
       </c>
       <c r="V6">
-        <v>0.1584</v>
+        <v>0.1449676823638043</v>
       </c>
       <c r="W6">
-        <v>0.01353383458646616</v>
+        <v>0.07804949480158149</v>
       </c>
       <c r="X6">
-        <v>0.02697665105782527</v>
+        <v>0.0565877606203216</v>
       </c>
       <c r="Y6">
-        <v>-0.01344281647135911</v>
+        <v>0.02146173418125989</v>
       </c>
       <c r="Z6">
-        <v>0.6172300981461286</v>
+        <v>0.3196820692442409</v>
       </c>
       <c r="AA6">
         <v>0</v>
       </c>
       <c r="AB6">
-        <v>0.02722795241121566</v>
+        <v>0.05574802001092969</v>
       </c>
       <c r="AC6">
-        <v>-0.02722795241121566</v>
+        <v>-0.05574802001092969</v>
       </c>
       <c r="AD6">
-        <v>1.08</v>
+        <v>129.9</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>1.08</v>
+        <v>129.9</v>
       </c>
       <c r="AG6">
-        <v>-2.88</v>
+        <v>67.10000000000001</v>
       </c>
       <c r="AH6">
-        <v>0.04141104294478528</v>
+        <v>0.2306872669152903</v>
       </c>
       <c r="AI6">
-        <v>0.04485049833887044</v>
+        <v>0.1716437632135307</v>
       </c>
       <c r="AJ6">
-        <v>-0.1301989150090416</v>
+        <v>0.1341195282830302</v>
       </c>
       <c r="AK6">
-        <v>-0.1431411530815109</v>
+        <v>0.09668587896253604</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Philippine Savings Bank (PSE:PSB)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0145</v>
-      </c>
-      <c r="E7">
-        <v>-0.16</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>20.3</v>
-      </c>
-      <c r="L7">
-        <v>0.09666666666666666</v>
-      </c>
-      <c r="M7">
-        <v>25.1</v>
-      </c>
-      <c r="N7">
-        <v>0.05228077483857529</v>
-      </c>
-      <c r="O7">
-        <v>1.236453201970443</v>
-      </c>
-      <c r="P7">
-        <v>25.1</v>
-      </c>
-      <c r="Q7">
-        <v>0.05228077483857529</v>
-      </c>
-      <c r="R7">
-        <v>1.236453201970443</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>57.3</v>
-      </c>
-      <c r="V7">
-        <v>0.1193501353884607</v>
-      </c>
-      <c r="W7">
-        <v>0.02821795941061996</v>
-      </c>
-      <c r="X7">
-        <v>0.02858956321062617</v>
-      </c>
-      <c r="Y7">
-        <v>-0.0003716038000062122</v>
-      </c>
-      <c r="Z7">
-        <v>0.2334111370456819</v>
-      </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0.02841169121685798</v>
-      </c>
-      <c r="AC7">
-        <v>-0.02841169121685798</v>
-      </c>
-      <c r="AD7">
-        <v>116.7</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>116.7</v>
-      </c>
-      <c r="AG7">
-        <v>59.40000000000001</v>
-      </c>
-      <c r="AH7">
-        <v>0.1955428954423592</v>
-      </c>
-      <c r="AI7">
-        <v>0.1459479739869935</v>
-      </c>
-      <c r="AJ7">
-        <v>0.1101019462465246</v>
-      </c>
-      <c r="AK7">
-        <v>0.08002155462750911</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Makati Finance Corporation (PSE:MFIN)</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>-0.0236</v>
-      </c>
-      <c r="E8">
-        <v>-0.126</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0.394</v>
-      </c>
-      <c r="L8">
-        <v>0.1545098039215687</v>
-      </c>
-      <c r="M8">
-        <v>0.032</v>
-      </c>
-      <c r="N8">
-        <v>0.002461538461538462</v>
-      </c>
-      <c r="O8">
-        <v>0.08121827411167512</v>
-      </c>
-      <c r="P8">
-        <v>0.032</v>
-      </c>
-      <c r="Q8">
-        <v>0.002461538461538462</v>
-      </c>
-      <c r="R8">
-        <v>0.08121827411167512</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-      <c r="U8">
-        <v>1.54</v>
-      </c>
-      <c r="V8">
-        <v>0.1184615384615385</v>
-      </c>
-      <c r="W8">
-        <v>0.03682242990654206</v>
-      </c>
-      <c r="X8">
-        <v>0.0341390064608925</v>
-      </c>
-      <c r="Y8">
-        <v>0.002683423445649563</v>
-      </c>
-      <c r="Z8">
-        <v>0.1028225806451613</v>
-      </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0.03258355451832744</v>
-      </c>
-      <c r="AC8">
-        <v>-0.03258355451832744</v>
-      </c>
-      <c r="AD8">
-        <v>12.1</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>12.1</v>
-      </c>
-      <c r="AG8">
-        <v>10.56</v>
-      </c>
-      <c r="AH8">
-        <v>0.4820717131474103</v>
-      </c>
-      <c r="AI8">
-        <v>0.5330396475770925</v>
-      </c>
-      <c r="AJ8">
-        <v>0.4482173174872665</v>
-      </c>
-      <c r="AK8">
-        <v>0.4990548204158791</v>
-      </c>
-      <c r="AL8">
-        <v>0</v>
-      </c>
-      <c r="AM8">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/philippines/philippines_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_financial_svcs_non_bank_insurance.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.05075</v>
+        <v>-0.04604999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.011</v>
+        <v>0.107</v>
       </c>
       <c r="G2">
-        <v>0.07767929443750296</v>
+        <v>0.7469451394176729</v>
       </c>
       <c r="H2">
-        <v>0.07767929443750296</v>
+        <v>0.7469451394176729</v>
       </c>
       <c r="I2">
-        <v>0.06668694145106387</v>
+        <v>0.72881540302404</v>
       </c>
       <c r="J2">
-        <v>0.05618045807840951</v>
+        <v>0.6815752226044641</v>
       </c>
       <c r="K2">
-        <v>67.75999999999999</v>
+        <v>38.92</v>
       </c>
       <c r="L2">
-        <v>0.2482806127870378</v>
+        <v>0.70560934044019</v>
       </c>
       <c r="M2">
-        <v>39.88</v>
+        <v>30.9</v>
       </c>
       <c r="N2">
-        <v>0.0570610960080126</v>
+        <v>0.05450696771917446</v>
       </c>
       <c r="O2">
-        <v>0.5885478158205432</v>
+        <v>0.7939362795477902</v>
       </c>
       <c r="P2">
-        <v>31.26</v>
+        <v>30.9</v>
       </c>
       <c r="Q2">
-        <v>0.04472742881671198</v>
+        <v>0.05450696771917446</v>
       </c>
       <c r="R2">
-        <v>0.4613341204250296</v>
+        <v>0.7939362795477902</v>
       </c>
       <c r="S2">
-        <v>8.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.216148445336008</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>82.12599999999999</v>
+        <v>55.002</v>
       </c>
       <c r="V2">
-        <v>0.1175075118042638</v>
+        <v>0.09702240254013055</v>
       </c>
       <c r="W2">
-        <v>0.04406206083362657</v>
+        <v>0.1651785714285715</v>
       </c>
       <c r="X2">
-        <v>0.05333114413526974</v>
+        <v>0.05651516509393059</v>
       </c>
       <c r="Y2">
-        <v>-0.009269083301643166</v>
+        <v>0.1086634063346409</v>
       </c>
       <c r="Z2">
-        <v>0.3155244790817642</v>
+        <v>0.3684101550237444</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>0.1341746498679088</v>
       </c>
       <c r="AB2">
-        <v>0.05333080955830185</v>
+        <v>0.05651340747529052</v>
       </c>
       <c r="AC2">
-        <v>-0.05332185234529718</v>
+        <v>0.07766124239261832</v>
       </c>
       <c r="AD2">
-        <v>130.295</v>
+        <v>83.44200000000001</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>130.295</v>
+        <v>83.44200000000001</v>
       </c>
       <c r="AG2">
-        <v>48.16900000000003</v>
+        <v>28.44</v>
       </c>
       <c r="AH2">
-        <v>0.1571343290782024</v>
+        <v>0.1283047996285032</v>
       </c>
       <c r="AI2">
-        <v>0.1500653609826607</v>
+        <v>0.3231655835353716</v>
       </c>
       <c r="AJ2">
-        <v>0.06447731066340597</v>
+        <v>0.04777102160110189</v>
       </c>
       <c r="AK2">
-        <v>0.06127365864889863</v>
+        <v>0.1399606299212598</v>
       </c>
       <c r="AL2">
-        <v>0.036</v>
+        <v>4.06</v>
       </c>
       <c r="AM2">
-        <v>-2.064</v>
+        <v>0.1229999999999993</v>
       </c>
       <c r="AN2">
-        <v>6.450247524752476</v>
+        <v>1.918206896551724</v>
       </c>
       <c r="AO2">
-        <v>505.5555555555556</v>
+        <v>9.901477832512317</v>
       </c>
       <c r="AP2">
-        <v>2.384603960396041</v>
+        <v>0.653793103448276</v>
       </c>
       <c r="AQ2">
-        <v>-8.81782945736434</v>
+        <v>326.8292682926847</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Philippine Stock Exchange, Inc. (PSE:PSE)</t>
+          <t>Citicore Energy REIT Corp. (PSE:CREIT)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,47 +721,41 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.0547</v>
-      </c>
-      <c r="E3">
-        <v>-0.011</v>
-      </c>
       <c r="G3">
-        <v>0.7114093959731543</v>
+        <v>0.8087248322147651</v>
       </c>
       <c r="H3">
-        <v>0.7114093959731543</v>
+        <v>0.8087248322147651</v>
       </c>
       <c r="I3">
-        <v>0.6107382550335571</v>
+        <v>0.936241610738255</v>
       </c>
       <c r="J3">
-        <v>0.4586833183422127</v>
+        <v>0.9306318986077984</v>
       </c>
       <c r="K3">
-        <v>14.7</v>
+        <v>24.1</v>
       </c>
       <c r="L3">
-        <v>0.4932885906040268</v>
+        <v>0.8087248322147651</v>
       </c>
       <c r="M3">
-        <v>9.460000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="N3">
-        <v>0.04086393088552916</v>
+        <v>0.05421487603305784</v>
       </c>
       <c r="O3">
-        <v>0.6435374149659865</v>
+        <v>0.6804979253112032</v>
       </c>
       <c r="P3">
-        <v>9.460000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="Q3">
-        <v>0.04086393088552916</v>
+        <v>0.05421487603305784</v>
       </c>
       <c r="R3">
-        <v>0.6435374149659865</v>
+        <v>0.6804979253112032</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>15.6</v>
+        <v>17.6</v>
       </c>
       <c r="V3">
-        <v>0.06738660907127429</v>
+        <v>0.05818181818181819</v>
       </c>
       <c r="W3">
-        <v>0.1402671755725191</v>
+        <v>0.3292349726775957</v>
       </c>
       <c r="X3">
-        <v>0.0533404359252423</v>
+        <v>0.06012171803812821</v>
       </c>
       <c r="Y3">
-        <v>0.08692673964727679</v>
+        <v>0.2691132546394674</v>
       </c>
       <c r="Z3">
-        <v>0.2983938799214964</v>
+        <v>0.4083870083595998</v>
       </c>
       <c r="AA3">
-        <v>0.1368682950153997</v>
+        <v>0.3800579769564532</v>
       </c>
       <c r="AB3">
-        <v>0.05333976677130652</v>
+        <v>0.05780248831024481</v>
       </c>
       <c r="AC3">
-        <v>0.08352852824409319</v>
+        <v>0.3222554886462084</v>
       </c>
       <c r="AD3">
-        <v>0.395</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.395</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="AG3">
-        <v>-15.205</v>
+        <v>65.30000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.001703357122835766</v>
+        <v>0.2151011935651272</v>
       </c>
       <c r="AI3">
-        <v>0.004394015240002225</v>
+        <v>0.5155472636815921</v>
       </c>
       <c r="AJ3">
-        <v>-0.07029751034466816</v>
+        <v>0.177542142468733</v>
       </c>
       <c r="AK3">
-        <v>-0.2046571101689212</v>
+        <v>0.4560055865921788</v>
       </c>
       <c r="AL3">
-        <v>0.036</v>
+        <v>4.02</v>
       </c>
       <c r="AM3">
-        <v>-2.064</v>
+        <v>3.722999999999999</v>
       </c>
       <c r="AN3">
-        <v>0.01955445544554455</v>
+        <v>2.848797250859107</v>
       </c>
       <c r="AO3">
-        <v>505.5555555555556</v>
+        <v>6.940298507462687</v>
       </c>
       <c r="AP3">
-        <v>-0.7527227722772277</v>
+        <v>2.243986254295533</v>
       </c>
       <c r="AQ3">
-        <v>-8.81782945736434</v>
+        <v>7.493956486704271</v>
       </c>
     </row>
     <row r="4">
@@ -847,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Citystate Savings Bank, Inc. (PSE:CSB)</t>
+          <t>The Philippine Stock Exchange, Inc. (PSE:PSE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,106 +850,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.102</v>
+        <v>0.0249</v>
+      </c>
+      <c r="E4">
+        <v>0.107</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>0.6758893280632411</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>0.6758893280632411</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>0.4861660079051384</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>0.3945424141076315</v>
       </c>
       <c r="K4">
-        <v>-0.267</v>
+        <v>14.8</v>
       </c>
       <c r="L4">
-        <v>-0.04635416666666667</v>
+        <v>0.5849802371541503</v>
       </c>
       <c r="M4">
-        <v>8.619999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="N4">
-        <v>0.3780701754385964</v>
+        <v>0.05783805345033905</v>
       </c>
       <c r="O4">
-        <v>-32.28464419475655</v>
+        <v>0.9797297297297297</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>14.5</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.05783805345033905</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>0.9797297297297297</v>
       </c>
       <c r="S4">
-        <v>8.619999999999999</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>3.72</v>
+        <v>37.4</v>
       </c>
       <c r="V4">
-        <v>0.1631578947368421</v>
+        <v>0.1491822895891504</v>
       </c>
       <c r="W4">
-        <v>-0.01160869565217391</v>
+        <v>0.1651785714285715</v>
       </c>
       <c r="X4">
-        <v>0.05332185234529718</v>
+        <v>0.05651516509393059</v>
       </c>
       <c r="Y4">
-        <v>-0.0649305479974711</v>
+        <v>0.1086634063346409</v>
       </c>
       <c r="Z4">
-        <v>0.2862823061630219</v>
+        <v>0.3400766180522885</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>0.1341746498679088</v>
       </c>
       <c r="AB4">
-        <v>0.05332185234529718</v>
+        <v>0.05651340747529052</v>
       </c>
       <c r="AC4">
-        <v>-0.05332185234529718</v>
+        <v>0.07766124239261832</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>0.542</v>
       </c>
       <c r="AG4">
-        <v>-3.72</v>
+        <v>-36.858</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.002157282619944118</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.005708748499083651</v>
       </c>
       <c r="AJ4">
-        <v>-0.1949685534591195</v>
+        <v>-0.1723609019743549</v>
       </c>
       <c r="AK4">
-        <v>-0.2403100775193799</v>
+        <v>-0.6405408223558443</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>-3.6</v>
+      </c>
+      <c r="AN4">
+        <v>0.03763888888888889</v>
+      </c>
+      <c r="AO4">
+        <v>307.5</v>
+      </c>
+      <c r="AP4">
+        <v>-2.559583333333333</v>
+      </c>
+      <c r="AQ4">
+        <v>-3.416666666666667</v>
       </c>
     </row>
     <row r="5">
@@ -975,10 +984,7 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.225</v>
-      </c>
-      <c r="E5">
-        <v>-0.305</v>
+        <v>-0.117</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,10 +999,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0.027</v>
+        <v>0.02</v>
       </c>
       <c r="L5">
-        <v>0.4736842105263158</v>
+        <v>0.3448275862068965</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1020,31 +1026,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.006</v>
+        <v>0.002</v>
       </c>
       <c r="V5">
-        <v>0.0005263157894736842</v>
+        <v>0.000145985401459854</v>
       </c>
       <c r="W5">
-        <v>0.01007462686567164</v>
+        <v>0.008474576271186441</v>
       </c>
       <c r="X5">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="Y5">
-        <v>-0.04324722547962554</v>
+        <v>-0.04801191089281927</v>
       </c>
       <c r="Z5">
-        <v>0.02130841121495327</v>
+        <v>0.02463891248937978</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.05332185234529718</v>
+        <v>0.05648648716400571</v>
       </c>
       <c r="AC5">
-        <v>-0.05332185234529718</v>
+        <v>-0.05648648716400571</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1056,7 +1062,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-0.006</v>
+        <v>-0.002</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1065,137 +1071,15 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-0.000526592943654555</v>
+        <v>-0.0001460067163089502</v>
       </c>
       <c r="AK5">
-        <v>-0.002548853016142736</v>
+        <v>-0.0008136696501220504</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Philippine Savings Bank (PSE:PSB)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.04679999999999999</v>
-      </c>
-      <c r="E6">
-        <v>0.0493</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>53.3</v>
-      </c>
-      <c r="L6">
-        <v>0.2246101980615255</v>
-      </c>
-      <c r="M6">
-        <v>21.8</v>
-      </c>
-      <c r="N6">
-        <v>0.05032317636195753</v>
-      </c>
-      <c r="O6">
-        <v>0.4090056285178237</v>
-      </c>
-      <c r="P6">
-        <v>21.8</v>
-      </c>
-      <c r="Q6">
-        <v>0.05032317636195753</v>
-      </c>
-      <c r="R6">
-        <v>0.4090056285178237</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>62.8</v>
-      </c>
-      <c r="V6">
-        <v>0.1449676823638043</v>
-      </c>
-      <c r="W6">
-        <v>0.07804949480158149</v>
-      </c>
-      <c r="X6">
-        <v>0.0565877606203216</v>
-      </c>
-      <c r="Y6">
-        <v>0.02146173418125989</v>
-      </c>
-      <c r="Z6">
-        <v>0.3196820692442409</v>
-      </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0.05574802001092969</v>
-      </c>
-      <c r="AC6">
-        <v>-0.05574802001092969</v>
-      </c>
-      <c r="AD6">
-        <v>129.9</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>129.9</v>
-      </c>
-      <c r="AG6">
-        <v>67.10000000000001</v>
-      </c>
-      <c r="AH6">
-        <v>0.2306872669152903</v>
-      </c>
-      <c r="AI6">
-        <v>0.1716437632135307</v>
-      </c>
-      <c r="AJ6">
-        <v>0.1341195282830302</v>
-      </c>
-      <c r="AK6">
-        <v>0.09668587896253604</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
         <v>0</v>
       </c>
     </row>
